--- a/jira_export_2026-09-22.xlsx
+++ b/jira_export_2026-09-22.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>41,969 €</t>
+          <t>42,172 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -770,7 +770,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>31,361 €</t>
+          <t>31,564 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>329 h</t>
+          <t>333 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -903,7 +903,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -952,7 +952,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -2104,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>2</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>516</v>
       </c>
       <c r="P38" s="15" t="n">
-        <v>55.78</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="39">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O88" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
+        <v>203.5</v>
       </c>
       <c r="P88" s="15" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
         <v>8</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>18</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L143" s="11" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>21</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>20.58</v>
+        <v>22.58</v>
       </c>
       <c r="L149" s="11" t="inlineStr"/>
       <c r="M149" s="11" t="inlineStr"/>
@@ -12793,13 +12793,13 @@
       <c r="L173" s="17" t="inlineStr"/>
       <c r="M173" s="17" t="inlineStr"/>
       <c r="N173" s="18" t="n">
-        <v>47315.375</v>
+        <v>46725.22500000001</v>
       </c>
       <c r="O173" s="18" t="n">
-        <v>41968.838</v>
+        <v>42172.338</v>
       </c>
       <c r="P173" s="18" t="n">
-        <v>197.44</v>
+        <v>194.95</v>
       </c>
     </row>
   </sheetData>
@@ -14054,16 +14054,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>111.92</v>
+        <v>113.67</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>39.42</v>
+        <v>41.42</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>15.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>166.58</v>
+        <v>170.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>24.17</v>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.1%</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>85.25</v>
+        <v>85.5</v>
       </c>
     </row>
   </sheetData>
@@ -14200,10 +14200,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>403837</v>
+        <v>403634</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>191467</v>
+        <v>191264</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>212370</v>
@@ -14250,10 +14250,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>230380</v>
+        <v>230177</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>117676</v>
+        <v>117473</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>112704</v>
@@ -14279,7 +14279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14303,7 +14303,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 24 commande(s)</t>
+          <t>Épics créées ce mois — 25 commande(s)</t>
         </is>
       </c>
     </row>
@@ -14358,12 +14358,12 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35857</t>
+          <t>PDMDEP-35872</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35853</t>
+          <t>PDMDEP-35863</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BOURG SAINT ANDEOL</t>
+          <t>COMMUNE DE DIJON</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00182113</t>
+          <t>00182115</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -14714,22 +14714,22 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35733</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35727</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIEUX BOUCAU</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -14749,11 +14749,11 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00181531</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>4815</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="14">
@@ -14849,22 +14849,22 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35857</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35853</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>MAIRIE DE BOURG SAINT ANDEOL</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -14884,42 +14884,42 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00182113</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>28915.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35687</t>
+          <t>PDMDEP-35733</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35683</t>
+          <t>PDMDEP-35727</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>COMMUNE DE VIEUX BOUCAU</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -14929,32 +14929,32 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>00181396</t>
+          <t>00181531</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>2333.33</v>
+        <v>4815</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35652</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35646</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GEX</t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -14974,32 +14974,32 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>00181167</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>6382.5</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35622</t>
+          <t>PDMDEP-35464</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35618</t>
+          <t>PDMDEP-35460</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Roche-sur-Yon</t>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -15019,32 +15019,32 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>00181123</t>
+          <t>00180631</t>
         </is>
       </c>
       <c r="I19" s="25" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35771</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35767</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -15064,32 +15064,32 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>00181751</t>
+          <t>0015489263</t>
         </is>
       </c>
       <c r="I20" s="26" t="n">
-        <v>2740</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35846</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35840</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -15109,32 +15109,32 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00182109</t>
         </is>
       </c>
       <c r="I21" s="25" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35719</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35715</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>Commune de Dunkerque</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -15154,11 +15154,11 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00181457</t>
         </is>
       </c>
       <c r="I22" s="26" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -15209,22 +15209,22 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35771</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35767</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -15244,32 +15244,32 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00181751</t>
         </is>
       </c>
       <c r="I24" s="26" t="n">
-        <v>0</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35846</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35840</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>00182109</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="I25" s="25" t="n">
@@ -15299,22 +15299,22 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -15334,32 +15334,32 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="I26" s="26" t="n">
-        <v>455</v>
+        <v>6382.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35439</t>
+          <t>PDMDEP-35687</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35683</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -15379,32 +15379,32 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>00180506</t>
+          <t>00181396</t>
         </is>
       </c>
       <c r="I27" s="25" t="n">
-        <v>3974</v>
+        <v>2333.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35719</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35715</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Commune de Dunkerque</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -15424,38 +15424,62 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>00181457</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I28" s="26" t="n">
-        <v>0</v>
+        <v>895</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>24 commande(s)</t>
-        </is>
-      </c>
-      <c r="I29" s="24" t="n">
-        <v>76336</v>
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35576</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35572</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>00180891</t>
+        </is>
+      </c>
+      <c r="I29" s="25" t="n">
+        <v>840</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B30" s="17" t="n"/>
@@ -15466,17 +15490,17 @@
       <c r="G30" s="17" t="n"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>12 commande(s)</t>
+          <t>25 commande(s)</t>
         </is>
       </c>
       <c r="I30" s="24" t="n">
-        <v>19032</v>
+        <v>76336</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B31" s="17" t="n"/>
@@ -15491,6 +15515,27 @@
         </is>
       </c>
       <c r="I31" s="24" t="n">
+        <v>19032</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>13 commande(s)</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="n">
         <v>57304</v>
       </c>
     </row>

--- a/jira_export_2026-09-22.xlsx
+++ b/jira_export_2026-09-22.xlsx
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>333 h</t>
+          <t>349 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>1033.24</v>
       </c>
       <c r="P15" s="12" t="n">
-        <v>375.72</v>
+        <v>258.31</v>
       </c>
     </row>
     <row r="16">
@@ -3816,7 +3816,7 @@
         <v>3</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1452.5</v>
       </c>
       <c r="P43" s="12" t="n">
-        <v>726.25</v>
+        <v>161.39</v>
       </c>
     </row>
     <row r="44">
@@ -8480,7 +8480,7 @@
         <v>8</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>10</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>10</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>10</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>10</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>10</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>10</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>11</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>36</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L163" s="11" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>42172.338</v>
       </c>
       <c r="P173" s="18" t="n">
-        <v>194.95</v>
+        <v>183.1</v>
       </c>
     </row>
   </sheetData>
@@ -14054,16 +14054,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>113.67</v>
+        <v>120.17</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>41.42</v>
+        <v>41.92</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>15.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>170.33</v>
+        <v>177.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>24.17</v>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>27.2%</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>41.75</v>
+        <v>48.75</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -14093,7 +14093,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>44.25</v>
+        <v>51.25</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>5.5</v>
@@ -14103,7 +14103,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>85.5</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
